--- a/.github/workflows/data/bian_records_mapping_v1.xlsx
+++ b/.github/workflows/data/bian_records_mapping_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\.github\workflows\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31C6D18-7BE0-41D2-80D1-195C377237F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA69A15C-78B2-45C0-BFD8-AD4BB8EBA6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>fileName</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>BQ - Quote</t>
+  </si>
+  <si>
+    <t>/payment-initiations/{paymentInitiationId}/quotes/{quoteId}/update</t>
   </si>
 </sst>
 </file>
@@ -413,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
@@ -482,6 +485,26 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
